--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 10,04</t>
+          <t>-19,97; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 15,19</t>
+          <t>-16,97; 13,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 23,28</t>
+          <t>-11,04; 22,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 12,63</t>
+          <t>-8,09; 11,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 18,89</t>
+          <t>-28,38; 18,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 27,73</t>
+          <t>-24,57; 23,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 57,15</t>
+          <t>-18,92; 56,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 15,26</t>
+          <t>-8,65; 13,77</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 2,97</t>
+          <t>-8,94; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 4,8</t>
+          <t>-9,33; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 6,31</t>
+          <t>-4,95; 6,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,45</t>
+          <t>-2,73; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 7,58</t>
+          <t>-20,49; 8,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 10,55</t>
+          <t>-18,73; 9,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 16,61</t>
+          <t>-11,31; 17,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,77</t>
+          <t>-2,86; 3,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 8,82</t>
+          <t>-11,68; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 9,56</t>
+          <t>-9,77; 9,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 10,7</t>
+          <t>-8,65; 10,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,7</t>
+          <t>-0,22; 2,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 28,1</t>
+          <t>-27,64; 27,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 25,74</t>
+          <t>-21,92; 26,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 32,48</t>
+          <t>-20,56; 31,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,79</t>
+          <t>-0,22; 3,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,74</t>
+          <t>-8,11; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,66</t>
+          <t>-6,86; 3,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,87</t>
+          <t>-3,21; 6,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,48</t>
+          <t>-1,76; 2,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 4,4</t>
+          <t>-17,91; 4,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 7,99</t>
+          <t>-13,63; 6,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 14,84</t>
+          <t>-7,5; 16,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,65</t>
+          <t>-1,84; 2,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 10,07</t>
+          <t>-20,56; 8,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 13,09</t>
+          <t>-14,86; 13,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 22,91</t>
+          <t>-11,71; 23,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 11,43</t>
+          <t>-7,89; 11,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 18,15</t>
+          <t>-30,03; 14,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 23,72</t>
+          <t>-21,55; 25,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 56,43</t>
+          <t>-19,66; 59,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 13,77</t>
+          <t>-8,57; 13,72</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 3,36</t>
+          <t>-9,12; 2,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,3</t>
+          <t>-8,74; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 6,61</t>
+          <t>-5,03; 6,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,1</t>
+          <t>-2,89; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 8,11</t>
+          <t>-20,64; 7,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 9,72</t>
+          <t>-17,01; 8,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 17,53</t>
+          <t>-11,18; 18,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,36</t>
+          <t>-3,09; 3,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 8,22</t>
+          <t>-12,15; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 9,83</t>
+          <t>-10,58; 10,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 10,68</t>
+          <t>-8,34; 11,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,94</t>
+          <t>-0,18; 2,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 27,56</t>
+          <t>-28,33; 23,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 26,08</t>
+          <t>-22,7; 28,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 31,64</t>
+          <t>-19,06; 33,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,03</t>
+          <t>-0,18; 2,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,82</t>
+          <t>-7,75; 1,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,27</t>
+          <t>-6,44; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,31</t>
+          <t>-3,27; 6,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,36</t>
+          <t>-1,79; 2,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 4,36</t>
+          <t>-17,4; 4,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,96</t>
+          <t>-12,96; 7,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,33</t>
+          <t>-7,5; 16,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,56</t>
+          <t>-1,86; 2,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 8,21</t>
+          <t>-19,96; 10,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 13,98</t>
+          <t>-15,55; 15,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 23,54</t>
+          <t>-9,45; 23,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 11,26</t>
+          <t>-8,9; 11,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 14,07</t>
+          <t>-28,6; 18,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 25,91</t>
+          <t>-22,83; 27,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,1</t>
+          <t>-16,85; 57,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 13,72</t>
+          <t>-9,7; 13,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>-0,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 2,94</t>
+          <t>-9,45; 2,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 4,02</t>
+          <t>-8,63; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,87</t>
+          <t>-5,81; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,0</t>
+          <t>-2,97; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 7,84</t>
+          <t>-21,18; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 8,77</t>
+          <t>-16,98; 10,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 18,49</t>
+          <t>-12,92; 16,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,21</t>
+          <t>-3,12; 3,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 7,75</t>
+          <t>-11,68; 8,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 10,3</t>
+          <t>-10,37; 9,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 11,6</t>
+          <t>-7,98; 10,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,79</t>
+          <t>-0,31; 2,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 23,94</t>
+          <t>-28,07; 28,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 28,21</t>
+          <t>-22,26; 25,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 33,81</t>
+          <t>-18,72; 32,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,87</t>
+          <t>-0,31; 2,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,86</t>
+          <t>-7,88; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,53</t>
+          <t>-6,47; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,24</t>
+          <t>-3,13; 5,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,36</t>
+          <t>-2,04; 2,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,67</t>
+          <t>-17,38; 4,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,64</t>
+          <t>-12,77; 7,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,02</t>
+          <t>-7,61; 14,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,52</t>
+          <t>-2,12; 2,36</t>
         </is>
       </c>
     </row>
